--- a/tools/importer/reports/import-general-v1.report.xlsx
+++ b/tools/importer/reports/import-general-v1.report.xlsx
@@ -73,7 +73,7 @@
     <t>en/home/who-we-are.report.json</t>
   </si>
   <si>
-    <t>["hero-text-up","default-content(intro)","columns(history,image-right)","section-metadata(yellow-intro)","columns(evert,image-left)","section-metadata(yellow-columns)","default-content(supporters)","cards-tiles"]</t>
+    <t>["hero-text-up","default-content(intro)","columns(history,image-right)","columns(evert,image-left)","section-metadata(yellow-band)","default-content(supporters)","cards-tiles","spacer(trailing-black-band)"]</t>
   </si>
   <si>
     <t>en/home/who-we-are</t>
@@ -82,7 +82,7 @@
     <t>general</t>
   </si>
   <si>
-    <t>2026-09-08T07:38:30.023Z</t>
+    <t>2026-09-08T08:34:00.217Z</t>
   </si>
   <si>
     <t>Who We Are</t>

--- a/tools/importer/reports/import-general-v1.report.xlsx
+++ b/tools/importer/reports/import-general-v1.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="418">
   <si>
     <t>_reportFile</t>
   </si>
@@ -70,10 +70,33 @@
     <t>https://www.ustafoundation.com/en/home.html</t>
   </si>
   <si>
+    <t>en/home/who-we-are.html.report.json</t>
+  </si>
+  <si>
+    <t>page.goto: Target page, context or browser has been closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.goto: Target page, context or browser has been closed
+    at processUrl (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:597:20)
+    at async main (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:954:22)</t>
+  </si>
+  <si>
+    <t>en/home/who-we-are.html</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-09-08T10:56:37.022Z</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/who-we-are.html</t>
+  </si>
+  <si>
     <t>en/home/who-we-are.report.json</t>
   </si>
   <si>
-    <t>["hero-text-up","default-content(intro)","columns(history,image-right)","columns(evert,image-left)","section-metadata(yellow-band)","default-content(supporters)","cards-tiles","spacer(trailing-black-band)"]</t>
+    <t>["hero-text-up","default-content(intro)","columns(history,image-right)","spacer(leading-yellow-strip)","columns(evert,image-left)","section-metadata(yellow-band)","default-content(supporters)","cards-tiles","spacer(trailing-black-band)"]</t>
   </si>
   <si>
     <t>en/home/who-we-are</t>
@@ -82,13 +105,10 @@
     <t>general</t>
   </si>
   <si>
-    <t>2026-09-08T08:34:00.217Z</t>
+    <t>2026-09-08T11:26:10.883Z</t>
   </si>
   <si>
     <t>Who We Are</t>
-  </si>
-  <si>
-    <t>https://www.ustafoundation.com/en/home/who-we-are.html</t>
   </si>
   <si>
     <t>en/home/news/2023-njtl-essay-contest-winners.report.json</t>
@@ -325,9 +345,6 @@
   </si>
   <si>
     <t>en/home/news/evert-speaks-on-rally-to-rebuild.html</t>
-  </si>
-  <si>
-    <t>failed</t>
   </si>
   <si>
     <t>2026-09-07T17:08:09.871Z</t>
@@ -1640,7 +1657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
@@ -1718,28 +1735,28 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
         <v>25</v>
@@ -1774,30 +1791,30 @@
         <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
         <v>36</v>
@@ -1829,7 +1846,7 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
@@ -1861,7 +1878,7 @@
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
         <v>48</v>
@@ -1893,7 +1910,7 @@
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
         <v>54</v>
@@ -1925,7 +1942,7 @@
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H9" t="s">
         <v>60</v>
@@ -1957,7 +1974,7 @@
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H10" t="s">
         <v>66</v>
@@ -1974,7 +1991,7 @@
         <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -1983,30 +2000,30 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F11" t="s">
         <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -2015,27 +2032,27 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
         <v>64</v>
@@ -2047,30 +2064,30 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -2085,7 +2102,7 @@
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H14" t="s">
         <v>87</v>
@@ -2102,7 +2119,7 @@
         <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -2111,30 +2128,30 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -2143,118 +2160,118 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
         <v>102</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" t="s">
         <v>103</v>
       </c>
-      <c r="F17" t="s">
+      <c r="I17" t="s">
         <v>104</v>
       </c>
-      <c r="G17" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="J17" t="s">
         <v>105</v>
-      </c>
-      <c r="I17" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
         <v>107</v>
       </c>
-      <c r="B18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I18" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="J18" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" t="s">
+        <v>115</v>
+      </c>
+      <c r="J19" t="s">
         <v>111</v>
-      </c>
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" t="s">
-        <v>112</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" t="s">
-        <v>29</v>
-      </c>
-      <c r="H19" t="s">
-        <v>113</v>
-      </c>
-      <c r="I19" t="s">
-        <v>114</v>
-      </c>
-      <c r="J19" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2262,7 +2279,7 @@
         <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -2277,7 +2294,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H20" t="s">
         <v>118</v>
@@ -2294,7 +2311,7 @@
         <v>121</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -2309,7 +2326,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H21" t="s">
         <v>123</v>
@@ -2326,7 +2343,7 @@
         <v>126</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -2341,7 +2358,7 @@
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H22" t="s">
         <v>128</v>
@@ -2373,7 +2390,7 @@
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H23" t="s">
         <v>133</v>
@@ -2390,7 +2407,7 @@
         <v>136</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -2405,7 +2422,7 @@
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H24" t="s">
         <v>138</v>
@@ -2422,39 +2439,39 @@
         <v>141</v>
       </c>
       <c r="B25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
         <v>142</v>
       </c>
-      <c r="C25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" t="s">
         <v>143</v>
       </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" t="s">
-        <v>29</v>
-      </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>144</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>145</v>
-      </c>
-      <c r="J25" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" t="s">
         <v>147</v>
-      </c>
-      <c r="B26" t="s">
-        <v>64</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -2469,7 +2486,7 @@
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H26" t="s">
         <v>149</v>
@@ -2486,7 +2503,7 @@
         <v>152</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -2501,7 +2518,7 @@
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H27" t="s">
         <v>154</v>
@@ -2518,7 +2535,7 @@
         <v>157</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
@@ -2533,7 +2550,7 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H28" t="s">
         <v>159</v>
@@ -2550,7 +2567,7 @@
         <v>162</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
@@ -2565,7 +2582,7 @@
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H29" t="s">
         <v>164</v>
@@ -2582,7 +2599,7 @@
         <v>167</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -2597,7 +2614,7 @@
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H30" t="s">
         <v>169</v>
@@ -2614,7 +2631,7 @@
         <v>172</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
@@ -2629,7 +2646,7 @@
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H31" t="s">
         <v>174</v>
@@ -2646,7 +2663,7 @@
         <v>177</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
@@ -2661,7 +2678,7 @@
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H32" t="s">
         <v>179</v>
@@ -2678,7 +2695,7 @@
         <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -2693,7 +2710,7 @@
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H33" t="s">
         <v>184</v>
@@ -2710,39 +2727,39 @@
         <v>187</v>
       </c>
       <c r="B34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
         <v>188</v>
       </c>
-      <c r="C34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H34" t="s">
         <v>189</v>
       </c>
-      <c r="F34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" t="s">
-        <v>29</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>191</v>
-      </c>
-      <c r="J34" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>192</v>
+      </c>
+      <c r="B35" t="s">
         <v>193</v>
-      </c>
-      <c r="B35" t="s">
-        <v>40</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
@@ -2757,7 +2774,7 @@
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H35" t="s">
         <v>195</v>
@@ -2774,7 +2791,7 @@
         <v>198</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
@@ -2789,7 +2806,7 @@
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H36" t="s">
         <v>200</v>
@@ -2806,7 +2823,7 @@
         <v>203</v>
       </c>
       <c r="B37" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
@@ -2821,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H37" t="s">
         <v>205</v>
@@ -2838,7 +2855,7 @@
         <v>208</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -2853,7 +2870,7 @@
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H38" t="s">
         <v>210</v>
@@ -2870,7 +2887,7 @@
         <v>213</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
@@ -2885,7 +2902,7 @@
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H39" t="s">
         <v>215</v>
@@ -2902,7 +2919,7 @@
         <v>218</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -2917,7 +2934,7 @@
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H40" t="s">
         <v>220</v>
@@ -2934,7 +2951,7 @@
         <v>223</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
@@ -2949,7 +2966,7 @@
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H41" t="s">
         <v>225</v>
@@ -2966,39 +2983,39 @@
         <v>228</v>
       </c>
       <c r="B42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
         <v>229</v>
       </c>
-      <c r="C42" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>35</v>
+      </c>
+      <c r="H42" t="s">
         <v>230</v>
       </c>
-      <c r="F42" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" t="s">
-        <v>29</v>
-      </c>
-      <c r="H42" t="s">
+      <c r="I42" t="s">
         <v>231</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>232</v>
-      </c>
-      <c r="J42" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>233</v>
+      </c>
+      <c r="B43" t="s">
         <v>234</v>
-      </c>
-      <c r="B43" t="s">
-        <v>64</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -3013,24 +3030,24 @@
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H43" t="s">
         <v>236</v>
       </c>
       <c r="I43" t="s">
-        <v>110</v>
+        <v>237</v>
       </c>
       <c r="J43" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -3039,19 +3056,19 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I44" t="s">
-        <v>241</v>
+        <v>115</v>
       </c>
       <c r="J44" t="s">
         <v>242</v>
@@ -3062,7 +3079,7 @@
         <v>243</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
@@ -3077,7 +3094,7 @@
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H45" t="s">
         <v>245</v>
@@ -3094,7 +3111,7 @@
         <v>248</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
@@ -3109,7 +3126,7 @@
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H46" t="s">
         <v>250</v>
@@ -3126,7 +3143,7 @@
         <v>253</v>
       </c>
       <c r="B47" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
@@ -3141,7 +3158,7 @@
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H47" t="s">
         <v>255</v>
@@ -3158,7 +3175,7 @@
         <v>258</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
@@ -3173,7 +3190,7 @@
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H48" t="s">
         <v>260</v>
@@ -3190,39 +3207,39 @@
         <v>263</v>
       </c>
       <c r="B49" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" t="s">
         <v>264</v>
       </c>
-      <c r="C49" t="s">
-        <v>12</v>
-      </c>
-      <c r="D49" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" t="s">
+        <v>35</v>
+      </c>
+      <c r="H49" t="s">
         <v>265</v>
       </c>
-      <c r="F49" t="s">
-        <v>14</v>
-      </c>
-      <c r="G49" t="s">
-        <v>29</v>
-      </c>
-      <c r="H49" t="s">
+      <c r="I49" t="s">
         <v>266</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>267</v>
-      </c>
-      <c r="J49" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>268</v>
+      </c>
+      <c r="B50" t="s">
         <v>269</v>
-      </c>
-      <c r="B50" t="s">
-        <v>64</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
@@ -3237,7 +3254,7 @@
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H50" t="s">
         <v>271</v>
@@ -3254,7 +3271,7 @@
         <v>274</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
@@ -3269,7 +3286,7 @@
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H51" t="s">
         <v>276</v>
@@ -3286,7 +3303,7 @@
         <v>279</v>
       </c>
       <c r="B52" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
@@ -3301,7 +3318,7 @@
         <v>14</v>
       </c>
       <c r="G52" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H52" t="s">
         <v>281</v>
@@ -3318,7 +3335,7 @@
         <v>284</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
@@ -3333,7 +3350,7 @@
         <v>14</v>
       </c>
       <c r="G53" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H53" t="s">
         <v>286</v>
@@ -3350,7 +3367,7 @@
         <v>289</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
@@ -3365,7 +3382,7 @@
         <v>14</v>
       </c>
       <c r="G54" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H54" t="s">
         <v>291</v>
@@ -3382,7 +3399,7 @@
         <v>294</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
@@ -3397,7 +3414,7 @@
         <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H55" t="s">
         <v>296</v>
@@ -3414,7 +3431,7 @@
         <v>299</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
@@ -3429,7 +3446,7 @@
         <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H56" t="s">
         <v>301</v>
@@ -3446,7 +3463,7 @@
         <v>304</v>
       </c>
       <c r="B57" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
@@ -3461,7 +3478,7 @@
         <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H57" t="s">
         <v>306</v>
@@ -3478,39 +3495,39 @@
         <v>309</v>
       </c>
       <c r="B58" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
         <v>310</v>
       </c>
-      <c r="C58" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s">
+        <v>35</v>
+      </c>
+      <c r="H58" t="s">
         <v>311</v>
       </c>
-      <c r="F58" t="s">
-        <v>14</v>
-      </c>
-      <c r="G58" t="s">
-        <v>29</v>
-      </c>
-      <c r="H58" t="s">
+      <c r="I58" t="s">
         <v>312</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" t="s">
         <v>313</v>
-      </c>
-      <c r="J58" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>314</v>
+      </c>
+      <c r="B59" t="s">
         <v>315</v>
-      </c>
-      <c r="B59" t="s">
-        <v>58</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
@@ -3525,7 +3542,7 @@
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H59" t="s">
         <v>317</v>
@@ -3542,7 +3559,7 @@
         <v>320</v>
       </c>
       <c r="B60" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C60" t="s">
         <v>12</v>
@@ -3557,7 +3574,7 @@
         <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H60" t="s">
         <v>322</v>
@@ -3589,7 +3606,7 @@
         <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H61" t="s">
         <v>327</v>
@@ -3606,39 +3623,39 @@
         <v>330</v>
       </c>
       <c r="B62" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
         <v>331</v>
       </c>
-      <c r="C62" t="s">
-        <v>12</v>
-      </c>
-      <c r="D62" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>35</v>
+      </c>
+      <c r="H62" t="s">
         <v>332</v>
       </c>
-      <c r="F62" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" t="s">
-        <v>29</v>
-      </c>
-      <c r="H62" t="s">
+      <c r="I62" t="s">
         <v>333</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>334</v>
-      </c>
-      <c r="J62" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>335</v>
+      </c>
+      <c r="B63" t="s">
         <v>336</v>
-      </c>
-      <c r="B63" t="s">
-        <v>188</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
@@ -3653,7 +3670,7 @@
         <v>14</v>
       </c>
       <c r="G63" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H63" t="s">
         <v>338</v>
@@ -3670,7 +3687,7 @@
         <v>341</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>193</v>
       </c>
       <c r="C64" t="s">
         <v>12</v>
@@ -3685,7 +3702,7 @@
         <v>14</v>
       </c>
       <c r="G64" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H64" t="s">
         <v>343</v>
@@ -3702,7 +3719,7 @@
         <v>346</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C65" t="s">
         <v>12</v>
@@ -3717,7 +3734,7 @@
         <v>14</v>
       </c>
       <c r="G65" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H65" t="s">
         <v>348</v>
@@ -3734,7 +3751,7 @@
         <v>351</v>
       </c>
       <c r="B66" t="s">
-        <v>264</v>
+        <v>40</v>
       </c>
       <c r="C66" t="s">
         <v>12</v>
@@ -3749,7 +3766,7 @@
         <v>14</v>
       </c>
       <c r="G66" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H66" t="s">
         <v>353</v>
@@ -3766,7 +3783,7 @@
         <v>356</v>
       </c>
       <c r="B67" t="s">
-        <v>64</v>
+        <v>269</v>
       </c>
       <c r="C67" t="s">
         <v>12</v>
@@ -3781,7 +3798,7 @@
         <v>14</v>
       </c>
       <c r="G67" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H67" t="s">
         <v>358</v>
@@ -3798,7 +3815,7 @@
         <v>361</v>
       </c>
       <c r="B68" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
@@ -3813,7 +3830,7 @@
         <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H68" t="s">
         <v>363</v>
@@ -3830,7 +3847,7 @@
         <v>366</v>
       </c>
       <c r="B69" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C69" t="s">
         <v>12</v>
@@ -3845,7 +3862,7 @@
         <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H69" t="s">
         <v>368</v>
@@ -3862,7 +3879,7 @@
         <v>371</v>
       </c>
       <c r="B70" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
@@ -3877,7 +3894,7 @@
         <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H70" t="s">
         <v>373</v>
@@ -3894,7 +3911,7 @@
         <v>376</v>
       </c>
       <c r="B71" t="s">
-        <v>188</v>
+        <v>40</v>
       </c>
       <c r="C71" t="s">
         <v>12</v>
@@ -3909,7 +3926,7 @@
         <v>14</v>
       </c>
       <c r="G71" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H71" t="s">
         <v>378</v>
@@ -3926,7 +3943,7 @@
         <v>381</v>
       </c>
       <c r="B72" t="s">
-        <v>64</v>
+        <v>193</v>
       </c>
       <c r="C72" t="s">
         <v>12</v>
@@ -3941,7 +3958,7 @@
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H72" t="s">
         <v>383</v>
@@ -3958,7 +3975,7 @@
         <v>386</v>
       </c>
       <c r="B73" t="s">
-        <v>188</v>
+        <v>70</v>
       </c>
       <c r="C73" t="s">
         <v>12</v>
@@ -3973,7 +3990,7 @@
         <v>14</v>
       </c>
       <c r="G73" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H73" t="s">
         <v>388</v>
@@ -3990,7 +4007,7 @@
         <v>391</v>
       </c>
       <c r="B74" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C74" t="s">
         <v>12</v>
@@ -4005,7 +4022,7 @@
         <v>14</v>
       </c>
       <c r="G74" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H74" t="s">
         <v>393</v>
@@ -4022,7 +4039,7 @@
         <v>396</v>
       </c>
       <c r="B75" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="C75" t="s">
         <v>12</v>
@@ -4037,7 +4054,7 @@
         <v>14</v>
       </c>
       <c r="G75" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H75" t="s">
         <v>398</v>
@@ -4054,7 +4071,7 @@
         <v>401</v>
       </c>
       <c r="B76" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="C76" t="s">
         <v>12</v>
@@ -4069,7 +4086,7 @@
         <v>14</v>
       </c>
       <c r="G76" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H76" t="s">
         <v>403</v>
@@ -4086,31 +4103,63 @@
         <v>406</v>
       </c>
       <c r="B77" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" t="s">
         <v>407</v>
       </c>
-      <c r="C77" t="s">
-        <v>12</v>
-      </c>
-      <c r="D77" t="s">
-        <v>12</v>
-      </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s">
+        <v>35</v>
+      </c>
+      <c r="H77" t="s">
         <v>408</v>
       </c>
-      <c r="F77" t="s">
-        <v>14</v>
-      </c>
-      <c r="G77" t="s">
+      <c r="I77" t="s">
         <v>409</v>
       </c>
-      <c r="H77" t="s">
+      <c r="J77" t="s">
         <v>410</v>
       </c>
-      <c r="I77" t="s">
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>411</v>
       </c>
-      <c r="J77" t="s">
+      <c r="B78" t="s">
         <v>412</v>
+      </c>
+      <c r="C78" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" t="s">
+        <v>413</v>
+      </c>
+      <c r="F78" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" t="s">
+        <v>414</v>
+      </c>
+      <c r="H78" t="s">
+        <v>415</v>
+      </c>
+      <c r="I78" t="s">
+        <v>416</v>
+      </c>
+      <c r="J78" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-general-v1.report.xlsx
+++ b/tools/importer/reports/import-general-v1.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="445">
   <si>
     <t>_reportFile</t>
   </si>
@@ -70,7 +70,46 @@
     <t>https://www.ustafoundation.com/en/home.html</t>
   </si>
   <si>
-    <t>en/home/who-we-are.html.report.json</t>
+    <t>en/home/get-involved.report.json</t>
+  </si>
+  <si>
+    <t>["hero-text-up","default-content(gift-intro)","columns(individual,image-right)","spacer(yellow-strip)","columns(impact,image-left,yellow)","columns(ypi,image-right)","spacer(yellow-strip)","columns(planned,image-left,yellow)","cards-content(signature-events)","spacer(yellow-strip)","columns(corporate,image-left,yellow,center-intro)","spacer(trailing-black-band)"]</t>
+  </si>
+  <si>
+    <t>en/home/get-involved</t>
+  </si>
+  <si>
+    <t>general</t>
+  </si>
+  <si>
+    <t>2026-09-08T13:54:39.144Z</t>
+  </si>
+  <si>
+    <t>Get Involved</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/get-involved.html</t>
+  </si>
+  <si>
+    <t>en/home/our-impact.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","default-content(not-ready-intro)","columns(not-ready-stats,image-right)","spacer(yellow-strip)","columns(reach,image-left,yellow,center-intro)","banner-stats-grid","spacer(yellow-strip)","cards-stats(yellow,center)","spacer(trailing-black-band)"]</t>
+  </si>
+  <si>
+    <t>en/home/our-impact</t>
+  </si>
+  <si>
+    <t>2026-09-08T18:00:46.773Z</t>
+  </si>
+  <si>
+    <t>Our Impact</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/our-impact.html</t>
+  </si>
+  <si>
+    <t>en/home/what-we-do.html.report.json</t>
   </si>
   <si>
     <t>page.goto: Target page, context or browser has been closed</t>
@@ -81,12 +120,39 @@
     at async main (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:954:22)</t>
   </si>
   <si>
+    <t>en/home/what-we-do.html</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-09-08T14:44:48.054Z</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/what-we-do.html</t>
+  </si>
+  <si>
+    <t>en/home/what-we-do.report.json</t>
+  </si>
+  <si>
+    <t>["hero-text-up","default-content(priorities-intro)","cards-content(priorities)","spacer(yellow-strip)","columns(transform,image-left,yellow,center-intro)","default-content(njtl-map)","default-content(sustained-intro)","cards-content(sustained)","spacer(trailing-black-band)"]</t>
+  </si>
+  <si>
+    <t>en/home/what-we-do</t>
+  </si>
+  <si>
+    <t>2026-09-08T14:52:38.566Z</t>
+  </si>
+  <si>
+    <t>What We Do</t>
+  </si>
+  <si>
+    <t>en/home/who-we-are.html.report.json</t>
+  </si>
+  <si>
     <t>en/home/who-we-are.html</t>
   </si>
   <si>
-    <t>failed</t>
-  </si>
-  <si>
     <t>2026-09-08T10:56:37.022Z</t>
   </si>
   <si>
@@ -102,13 +168,28 @@
     <t>en/home/who-we-are</t>
   </si>
   <si>
-    <t>general</t>
-  </si>
-  <si>
-    <t>2026-09-08T11:26:10.883Z</t>
+    <t>2026-09-08T18:51:42.954Z</t>
   </si>
   <si>
     <t>Who We Are</t>
+  </si>
+  <si>
+    <t>en/home/get-involved/special-funds.report.json</t>
+  </si>
+  <si>
+    <t>["hero-text-up","fund(tiafoe,image-right,center-intro)","spacer(yellow-strip)","fund(mackie,image-left,yellow)","fund(evert,image-right,center-intro)","spacer(above-cards-expand)","cards-expand","spacer(trailing-black-band)"]</t>
+  </si>
+  <si>
+    <t>en/home/get-involved/special-funds</t>
+  </si>
+  <si>
+    <t>2026-09-08T18:35:58.380Z</t>
+  </si>
+  <si>
+    <t>Special Funds</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/get-involved/special-funds.html</t>
   </si>
   <si>
     <t>en/home/news/2023-njtl-essay-contest-winners.report.json</t>
@@ -1657,7 +1738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
@@ -1735,28 +1816,28 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>12</v>
       </c>
       <c r="J3" t="s">
         <v>25</v>
@@ -1782,16 +1863,16 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>30</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>31</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1799,28 +1880,28 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="J5" t="s">
         <v>38</v>
@@ -1846,7 +1927,7 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
@@ -1855,239 +1936,239 @@
         <v>43</v>
       </c>
       <c r="J6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
         <v>45</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="I7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" t="s">
         <v>47</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" t="s">
         <v>51</v>
       </c>
-      <c r="B8" t="s">
+      <c r="I8" t="s">
         <v>52</v>
       </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" t="s">
-        <v>55</v>
-      </c>
       <c r="J8" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" t="s">
         <v>57</v>
       </c>
-      <c r="B9" t="s">
+      <c r="J9" t="s">
         <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" t="s">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
+      <c r="I10" t="s">
         <v>64</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="J10" t="s">
         <v>65</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" t="s">
         <v>69</v>
       </c>
-      <c r="B11" t="s">
+      <c r="I11" t="s">
         <v>70</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="J11" t="s">
         <v>71</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" t="s">
-        <v>72</v>
-      </c>
-      <c r="I11" t="s">
-        <v>73</v>
-      </c>
-      <c r="J11" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" t="s">
         <v>75</v>
       </c>
-      <c r="B12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="I12" t="s">
         <v>76</v>
       </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>77</v>
-      </c>
-      <c r="I12" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
         <v>80</v>
       </c>
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" t="s">
         <v>81</v>
       </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>82</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>83</v>
-      </c>
-      <c r="J13" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
         <v>85</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -2102,7 +2183,7 @@
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H14" t="s">
         <v>87</v>
@@ -2134,7 +2215,7 @@
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H15" t="s">
         <v>93</v>
@@ -2151,7 +2232,7 @@
         <v>96</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -2160,30 +2241,30 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -2192,51 +2273,51 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
         <v>108</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" t="s">
         <v>109</v>
       </c>
-      <c r="F18" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>110</v>
-      </c>
-      <c r="I18" t="s">
-        <v>12</v>
       </c>
       <c r="J18" t="s">
         <v>111</v>
@@ -2247,7 +2328,7 @@
         <v>112</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -2262,7 +2343,7 @@
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H19" t="s">
         <v>114</v>
@@ -2271,15 +2352,15 @@
         <v>115</v>
       </c>
       <c r="J19" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -2288,30 +2369,30 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F20" t="s">
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -2320,30 +2401,30 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I21" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J21" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -2352,62 +2433,62 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I22" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J22" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>135</v>
       </c>
       <c r="E23" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H23" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I23" t="s">
-        <v>134</v>
+        <v>12</v>
       </c>
       <c r="J23" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -2416,30 +2497,30 @@
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F24" t="s">
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H24" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" t="s">
+        <v>142</v>
+      </c>
+      <c r="J24" t="s">
         <v>138</v>
-      </c>
-      <c r="I24" t="s">
-        <v>139</v>
-      </c>
-      <c r="J24" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
@@ -2448,30 +2529,30 @@
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H25" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I25" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J25" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -2480,30 +2561,30 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -2512,30 +2593,30 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
@@ -2544,30 +2625,30 @@
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
@@ -2576,30 +2657,30 @@
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -2608,30 +2689,30 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
@@ -2640,30 +2721,30 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H31" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I31" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
@@ -2672,30 +2753,30 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H32" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I32" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J32" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -2704,30 +2785,30 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
@@ -2736,30 +2817,30 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I34" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J34" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B35" t="s">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
@@ -2768,30 +2849,30 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H35" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I35" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J35" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
@@ -2800,30 +2881,30 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F36" t="s">
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I36" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
@@ -2832,30 +2913,30 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H37" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J37" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -2864,30 +2945,30 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H38" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I38" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J38" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
@@ -2896,30 +2977,30 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H39" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J39" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B40" t="s">
-        <v>147</v>
+        <v>220</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -2928,30 +3009,30 @@
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H40" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I40" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J40" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B41" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
@@ -2960,30 +3041,30 @@
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H41" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I41" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J41" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
@@ -2992,30 +3073,30 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H42" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I42" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J42" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B43" t="s">
-        <v>234</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -3024,30 +3105,30 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H43" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I43" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J43" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -3056,30 +3137,30 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H44" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
+        <v>243</v>
       </c>
       <c r="J44" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
@@ -3088,30 +3169,30 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H45" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I45" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J45" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
@@ -3120,30 +3201,30 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H46" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I46" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J46" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
@@ -3152,30 +3233,30 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H47" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I47" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J47" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>261</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
@@ -3184,30 +3265,30 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H48" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="I48" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J48" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C49" t="s">
         <v>12</v>
@@ -3216,30 +3297,30 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H49" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I49" t="s">
-        <v>266</v>
+        <v>142</v>
       </c>
       <c r="J49" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B50" t="s">
-        <v>269</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
@@ -3248,30 +3329,30 @@
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
@@ -3280,30 +3361,30 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H51" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I51" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
@@ -3312,30 +3393,30 @@
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F52" t="s">
         <v>14</v>
       </c>
       <c r="G52" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H52" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I52" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J52" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
@@ -3344,30 +3425,30 @@
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F53" t="s">
         <v>14</v>
       </c>
       <c r="G53" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H53" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I53" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J53" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
@@ -3376,30 +3457,30 @@
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F54" t="s">
         <v>14</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H54" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I54" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J54" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>296</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
@@ -3408,30 +3489,30 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H55" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I55" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J55" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
@@ -3440,30 +3521,30 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F56" t="s">
         <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H56" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="I56" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J56" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
@@ -3472,30 +3553,30 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F57" t="s">
         <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H57" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I57" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J57" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="C58" t="s">
         <v>12</v>
@@ -3504,30 +3585,30 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H58" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I58" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J58" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B59" t="s">
-        <v>315</v>
+        <v>97</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
@@ -3536,30 +3617,30 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H59" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I59" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J59" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C60" t="s">
         <v>12</v>
@@ -3568,30 +3649,30 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J60" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B61" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
@@ -3600,30 +3681,30 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F61" t="s">
         <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H61" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I61" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J61" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C62" t="s">
         <v>12</v>
@@ -3632,30 +3713,30 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F62" t="s">
         <v>14</v>
       </c>
       <c r="G62" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H62" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I62" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J62" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B63" t="s">
-        <v>336</v>
+        <v>67</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
@@ -3670,7 +3751,7 @@
         <v>14</v>
       </c>
       <c r="G63" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H63" t="s">
         <v>338</v>
@@ -3687,7 +3768,7 @@
         <v>341</v>
       </c>
       <c r="B64" t="s">
-        <v>193</v>
+        <v>342</v>
       </c>
       <c r="C64" t="s">
         <v>12</v>
@@ -3696,30 +3777,30 @@
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F64" t="s">
         <v>14</v>
       </c>
       <c r="G64" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H64" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I64" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J64" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B65" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="C65" t="s">
         <v>12</v>
@@ -3728,30 +3809,30 @@
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F65" t="s">
         <v>14</v>
       </c>
       <c r="G65" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H65" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I65" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J65" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B66" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="C66" t="s">
         <v>12</v>
@@ -3760,30 +3841,30 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F66" t="s">
         <v>14</v>
       </c>
       <c r="G66" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H66" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I66" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J66" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B67" t="s">
-        <v>269</v>
+        <v>97</v>
       </c>
       <c r="C67" t="s">
         <v>12</v>
@@ -3792,30 +3873,30 @@
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F67" t="s">
         <v>14</v>
       </c>
       <c r="G67" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H67" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I67" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J67" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>363</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
@@ -3824,30 +3905,30 @@
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F68" t="s">
         <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H68" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I68" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J68" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="C69" t="s">
         <v>12</v>
@@ -3856,30 +3937,30 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F69" t="s">
         <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H69" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I69" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J69" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B70" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
@@ -3888,30 +3969,30 @@
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F70" t="s">
         <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H70" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I70" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J70" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B71" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C71" t="s">
         <v>12</v>
@@ -3920,30 +4001,30 @@
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F71" t="s">
         <v>14</v>
       </c>
       <c r="G71" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H71" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="I71" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J71" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B72" t="s">
-        <v>193</v>
+        <v>296</v>
       </c>
       <c r="C72" t="s">
         <v>12</v>
@@ -3952,30 +4033,30 @@
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F72" t="s">
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H72" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I72" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J72" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C73" t="s">
         <v>12</v>
@@ -3984,30 +4065,30 @@
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F73" t="s">
         <v>14</v>
       </c>
       <c r="G73" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H73" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I73" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J73" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B74" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="C74" t="s">
         <v>12</v>
@@ -4016,30 +4097,30 @@
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F74" t="s">
         <v>14</v>
       </c>
       <c r="G74" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H74" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I74" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J74" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B75" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="C75" t="s">
         <v>12</v>
@@ -4048,30 +4129,30 @@
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F75" t="s">
         <v>14</v>
       </c>
       <c r="G75" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H75" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I75" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J75" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B76" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C76" t="s">
         <v>12</v>
@@ -4080,30 +4161,30 @@
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F76" t="s">
         <v>14</v>
       </c>
       <c r="G76" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H76" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I76" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J76" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B77" t="s">
-        <v>46</v>
+        <v>220</v>
       </c>
       <c r="C77" t="s">
         <v>12</v>
@@ -4112,30 +4193,30 @@
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F77" t="s">
         <v>14</v>
       </c>
       <c r="G77" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H77" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I77" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J77" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B78" t="s">
-        <v>412</v>
+        <v>97</v>
       </c>
       <c r="C78" t="s">
         <v>12</v>
@@ -4144,13 +4225,13 @@
         <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F78" t="s">
         <v>14</v>
       </c>
       <c r="G78" t="s">
-        <v>414</v>
+        <v>62</v>
       </c>
       <c r="H78" t="s">
         <v>415</v>
@@ -4160,6 +4241,166 @@
       </c>
       <c r="J78" t="s">
         <v>417</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>418</v>
+      </c>
+      <c r="B79" t="s">
+        <v>220</v>
+      </c>
+      <c r="C79" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" t="s">
+        <v>419</v>
+      </c>
+      <c r="F79" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" t="s">
+        <v>62</v>
+      </c>
+      <c r="H79" t="s">
+        <v>420</v>
+      </c>
+      <c r="I79" t="s">
+        <v>421</v>
+      </c>
+      <c r="J79" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>423</v>
+      </c>
+      <c r="B80" t="s">
+        <v>220</v>
+      </c>
+      <c r="C80" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" t="s">
+        <v>424</v>
+      </c>
+      <c r="F80" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" t="s">
+        <v>62</v>
+      </c>
+      <c r="H80" t="s">
+        <v>425</v>
+      </c>
+      <c r="I80" t="s">
+        <v>426</v>
+      </c>
+      <c r="J80" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>428</v>
+      </c>
+      <c r="B81" t="s">
+        <v>118</v>
+      </c>
+      <c r="C81" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" t="s">
+        <v>429</v>
+      </c>
+      <c r="F81" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" t="s">
+        <v>62</v>
+      </c>
+      <c r="H81" t="s">
+        <v>430</v>
+      </c>
+      <c r="I81" t="s">
+        <v>431</v>
+      </c>
+      <c r="J81" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>433</v>
+      </c>
+      <c r="B82" t="s">
+        <v>73</v>
+      </c>
+      <c r="C82" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82" t="s">
+        <v>434</v>
+      </c>
+      <c r="F82" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" t="s">
+        <v>62</v>
+      </c>
+      <c r="H82" t="s">
+        <v>435</v>
+      </c>
+      <c r="I82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J82" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>438</v>
+      </c>
+      <c r="B83" t="s">
+        <v>439</v>
+      </c>
+      <c r="C83" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" t="s">
+        <v>440</v>
+      </c>
+      <c r="F83" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" t="s">
+        <v>441</v>
+      </c>
+      <c r="H83" t="s">
+        <v>442</v>
+      </c>
+      <c r="I83" t="s">
+        <v>443</v>
+      </c>
+      <c r="J83" t="s">
+        <v>444</v>
       </c>
     </row>
   </sheetData>
